--- a/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.256221227681215</v>
+        <v>1.270554744163218</v>
       </c>
       <c r="C3" t="n">
-        <v>4.598856621682637</v>
+        <v>4.590727750691474</v>
       </c>
       <c r="D3" t="n">
-        <v>6.110363443997139</v>
+        <v>6.044507807996263</v>
       </c>
       <c r="E3" t="n">
-        <v>11.96544129336099</v>
+        <v>11.90579030285095</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387262204527178</v>
+        <v>1.417323761420035</v>
       </c>
       <c r="C4" t="n">
-        <v>5.024417700632892</v>
+        <v>4.99862199594841</v>
       </c>
       <c r="D4" t="n">
-        <v>6.396131185392364</v>
+        <v>6.277861246481265</v>
       </c>
       <c r="E4" t="n">
-        <v>12.80781109055243</v>
+        <v>12.69380700384971</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.561680215156942</v>
+        <v>1.611292030912394</v>
       </c>
       <c r="C5" t="n">
-        <v>5.529848281268659</v>
+        <v>5.477472720196169</v>
       </c>
       <c r="D5" t="n">
-        <v>6.710093006287811</v>
+        <v>6.52289060113151</v>
       </c>
       <c r="E5" t="n">
-        <v>13.80162150271341</v>
+        <v>13.61165535224007</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.762462434688269</v>
+        <v>1.849588003361049</v>
       </c>
       <c r="C6" t="n">
-        <v>6.152011950081803</v>
+        <v>6.023284985554023</v>
       </c>
       <c r="D6" t="n">
-        <v>7.033174627205945</v>
+        <v>6.886837879377995</v>
       </c>
       <c r="E6" t="n">
-        <v>14.94764901197602</v>
+        <v>14.75971086829307</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.983094981989981</v>
+        <v>2.124849791820175</v>
       </c>
       <c r="C7" t="n">
-        <v>6.880710280645821</v>
+        <v>6.649513189742351</v>
       </c>
       <c r="D7" t="n">
-        <v>7.48307836545669</v>
+        <v>7.222616590625661</v>
       </c>
       <c r="E7" t="n">
-        <v>16.34688362809249</v>
+        <v>15.99697957218819</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.206389272686726</v>
+        <v>1.35344929233768</v>
       </c>
       <c r="C8" t="n">
-        <v>4.548070151504987</v>
+        <v>4.24016855265474</v>
       </c>
       <c r="D8" t="n">
-        <v>5.667551955235377</v>
+        <v>5.566349062047703</v>
       </c>
       <c r="E8" t="n">
-        <v>11.42201137942709</v>
+        <v>11.15996690704012</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.515355641458267</v>
+        <v>1.732813828374343</v>
       </c>
       <c r="C9" t="n">
-        <v>5.535632221735035</v>
+        <v>5.066449186560606</v>
       </c>
       <c r="D9" t="n">
-        <v>6.160260685897388</v>
+        <v>6.133408368439207</v>
       </c>
       <c r="E9" t="n">
-        <v>13.21124854909069</v>
+        <v>12.93267138337416</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.839741315075229</v>
+        <v>2.162735097255696</v>
       </c>
       <c r="C10" t="n">
-        <v>6.669815438849601</v>
+        <v>6.041002983434161</v>
       </c>
       <c r="D10" t="n">
-        <v>6.686089769704395</v>
+        <v>6.801983873673999</v>
       </c>
       <c r="E10" t="n">
-        <v>15.19564652362923</v>
+        <v>15.00572195436386</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.177261297580924</v>
+        <v>2.628990651261259</v>
       </c>
       <c r="C11" t="n">
-        <v>7.913796412413259</v>
+        <v>7.105166923591553</v>
       </c>
       <c r="D11" t="n">
-        <v>7.197863851786323</v>
+        <v>7.396801484731173</v>
       </c>
       <c r="E11" t="n">
-        <v>17.2889215617805</v>
+        <v>17.13095905958399</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.525757041024297</v>
+        <v>3.121641907008302</v>
       </c>
       <c r="C12" t="n">
-        <v>9.228970169677696</v>
+        <v>8.279300755187533</v>
       </c>
       <c r="D12" t="n">
-        <v>7.723749114568458</v>
+        <v>7.940729273951996</v>
       </c>
       <c r="E12" t="n">
-        <v>19.47847632527045</v>
+        <v>19.34167193614783</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.87518829766098</v>
+        <v>3.610504190352613</v>
       </c>
       <c r="C13" t="n">
-        <v>10.63494655924587</v>
+        <v>9.534196040635106</v>
       </c>
       <c r="D13" t="n">
-        <v>8.190328429902001</v>
+        <v>8.517371022819226</v>
       </c>
       <c r="E13" t="n">
-        <v>21.70046328680885</v>
+        <v>21.66207125380695</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.676275300139174</v>
+        <v>2.077967190808799</v>
       </c>
       <c r="C14" t="n">
-        <v>7.498166813524312</v>
+        <v>6.786910236751583</v>
       </c>
       <c r="D14" t="n">
-        <v>6.217889267370131</v>
+        <v>6.526727460172093</v>
       </c>
       <c r="E14" t="n">
-        <v>15.39233138103362</v>
+        <v>15.39160488773247</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.727237823466626</v>
+        <v>2.197612783525358</v>
       </c>
       <c r="C15" t="n">
-        <v>8.086528212679426</v>
+        <v>7.310613732105001</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239173557598202</v>
+        <v>6.620739620330768</v>
       </c>
       <c r="E15" t="n">
-        <v>16.05293959374425</v>
+        <v>16.12896613596113</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.032050850681176</v>
+        <v>2.611851409855257</v>
       </c>
       <c r="C16" t="n">
-        <v>9.569409032559019</v>
+        <v>8.678060656919255</v>
       </c>
       <c r="D16" t="n">
-        <v>6.793880645451735</v>
+        <v>7.238749800154134</v>
       </c>
       <c r="E16" t="n">
-        <v>18.39534052869193</v>
+        <v>18.52866186692865</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.649493222767321</v>
+        <v>2.132591633073092</v>
       </c>
       <c r="C17" t="n">
-        <v>8.893868437266789</v>
+        <v>8.125670493647746</v>
       </c>
       <c r="D17" t="n">
-        <v>6.33689672407893</v>
+        <v>6.804188996346327</v>
       </c>
       <c r="E17" t="n">
-        <v>16.88025838411304</v>
+        <v>17.06245112306717</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.907810678708742</v>
+        <v>2.476537123778919</v>
       </c>
       <c r="C18" t="n">
-        <v>10.37902691182024</v>
+        <v>9.551806296221875</v>
       </c>
       <c r="D18" t="n">
-        <v>6.77238037072873</v>
+        <v>7.311448217653611</v>
       </c>
       <c r="E18" t="n">
-        <v>19.05921796125771</v>
+        <v>19.3397916376544</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.939305145060979</v>
+        <v>2.526449177062827</v>
       </c>
       <c r="C19" t="n">
-        <v>11.11784114665117</v>
+        <v>10.3060143350554</v>
       </c>
       <c r="D19" t="n">
-        <v>6.900753700536042</v>
+        <v>7.472160316838814</v>
       </c>
       <c r="E19" t="n">
-        <v>19.95789999224819</v>
+        <v>20.30462382895704</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.195286041466293</v>
+        <v>2.858584242886566</v>
       </c>
       <c r="C20" t="n">
-        <v>12.85438593835406</v>
+        <v>11.99350119397707</v>
       </c>
       <c r="D20" t="n">
-        <v>7.426685763178101</v>
+        <v>7.968944290141785</v>
       </c>
       <c r="E20" t="n">
-        <v>22.47635774299845</v>
+        <v>22.82102972700542</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.326488410593078</v>
+        <v>1.722338902422434</v>
       </c>
       <c r="C21" t="n">
-        <v>9.525407100454679</v>
+        <v>8.960470201522895</v>
       </c>
       <c r="D21" t="n">
-        <v>6.209053538031911</v>
+        <v>6.677219565756088</v>
       </c>
       <c r="E21" t="n">
-        <v>17.06094904907967</v>
+        <v>17.36002866970142</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.270554744163218</v>
+        <v>1.255298384839223</v>
       </c>
       <c r="C3" t="n">
-        <v>4.590727750691474</v>
+        <v>4.577483974161185</v>
       </c>
       <c r="D3" t="n">
-        <v>6.044507807996263</v>
+        <v>6.059204571128838</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90579030285095</v>
+        <v>11.89198693012925</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.417323761420035</v>
+        <v>1.373608914020839</v>
       </c>
       <c r="C4" t="n">
-        <v>4.99862199594841</v>
+        <v>4.987344346203179</v>
       </c>
       <c r="D4" t="n">
-        <v>6.277861246481265</v>
+        <v>6.284802482499808</v>
       </c>
       <c r="E4" t="n">
-        <v>12.69380700384971</v>
+        <v>12.64575574272383</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.611292030912394</v>
+        <v>1.541305363180241</v>
       </c>
       <c r="C5" t="n">
-        <v>5.477472720196169</v>
+        <v>5.499599223718398</v>
       </c>
       <c r="D5" t="n">
-        <v>6.52289060113151</v>
+        <v>6.68553925773211</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61165535224007</v>
+        <v>13.72644384463075</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.849588003361049</v>
+        <v>1.736343191290071</v>
       </c>
       <c r="C6" t="n">
-        <v>6.023284985554023</v>
+        <v>6.114781582086863</v>
       </c>
       <c r="D6" t="n">
-        <v>6.886837879377995</v>
+        <v>7.01074124757204</v>
       </c>
       <c r="E6" t="n">
-        <v>14.75971086829307</v>
+        <v>14.86186602094897</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.124849791820175</v>
+        <v>1.960885738193804</v>
       </c>
       <c r="C7" t="n">
-        <v>6.649513189742351</v>
+        <v>6.845507867957046</v>
       </c>
       <c r="D7" t="n">
-        <v>7.222616590625661</v>
+        <v>7.391337445898849</v>
       </c>
       <c r="E7" t="n">
-        <v>15.99697957218819</v>
+        <v>16.1977310520497</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.35344929233768</v>
+        <v>1.203194432006626</v>
       </c>
       <c r="C8" t="n">
-        <v>4.24016855265474</v>
+        <v>4.48991607005977</v>
       </c>
       <c r="D8" t="n">
-        <v>5.566349062047703</v>
+        <v>5.594926502702007</v>
       </c>
       <c r="E8" t="n">
-        <v>11.15996690704012</v>
+        <v>11.2880370047684</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.732813828374343</v>
+        <v>1.532094150949512</v>
       </c>
       <c r="C9" t="n">
-        <v>5.066449186560606</v>
+        <v>5.406742859549266</v>
       </c>
       <c r="D9" t="n">
-        <v>6.133408368439207</v>
+        <v>6.116643837009071</v>
       </c>
       <c r="E9" t="n">
-        <v>12.93267138337416</v>
+        <v>13.05548084750785</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.162735097255696</v>
+        <v>1.89154343689195</v>
       </c>
       <c r="C10" t="n">
-        <v>6.041002983434161</v>
+        <v>6.507998179385404</v>
       </c>
       <c r="D10" t="n">
-        <v>6.801983873673999</v>
+        <v>6.675835619135677</v>
       </c>
       <c r="E10" t="n">
-        <v>15.00572195436386</v>
+        <v>15.07537723541303</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.628990651261259</v>
+        <v>2.259165648631219</v>
       </c>
       <c r="C11" t="n">
-        <v>7.105166923591553</v>
+        <v>7.774111961284961</v>
       </c>
       <c r="D11" t="n">
-        <v>7.396801484731173</v>
+        <v>7.221099829726083</v>
       </c>
       <c r="E11" t="n">
-        <v>17.13095905958399</v>
+        <v>17.25437743964226</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.121641907008302</v>
+        <v>2.644824784325983</v>
       </c>
       <c r="C12" t="n">
-        <v>8.279300755187533</v>
+        <v>9.233037132420291</v>
       </c>
       <c r="D12" t="n">
-        <v>7.940729273951996</v>
+        <v>7.750260484115673</v>
       </c>
       <c r="E12" t="n">
-        <v>19.34167193614783</v>
+        <v>19.62812240086195</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.610504190352613</v>
+        <v>3.018053089559555</v>
       </c>
       <c r="C13" t="n">
-        <v>9.534196040635106</v>
+        <v>10.83037567169537</v>
       </c>
       <c r="D13" t="n">
-        <v>8.517371022819226</v>
+        <v>8.248282187601486</v>
       </c>
       <c r="E13" t="n">
-        <v>21.66207125380695</v>
+        <v>22.09671094885641</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.077967190808799</v>
+        <v>1.742906516826405</v>
       </c>
       <c r="C14" t="n">
-        <v>6.786910236751583</v>
+        <v>7.757682001664914</v>
       </c>
       <c r="D14" t="n">
-        <v>6.526727460172093</v>
+        <v>6.280298968929101</v>
       </c>
       <c r="E14" t="n">
-        <v>15.39160488773247</v>
+        <v>15.78088748742042</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.197612783525358</v>
+        <v>1.798689421381709</v>
       </c>
       <c r="C15" t="n">
-        <v>7.310613732105001</v>
+        <v>8.598745259893155</v>
       </c>
       <c r="D15" t="n">
-        <v>6.620739620330768</v>
+        <v>6.319470702328549</v>
       </c>
       <c r="E15" t="n">
-        <v>16.12896613596113</v>
+        <v>16.71690538360341</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.611851409855257</v>
+        <v>2.099447830577719</v>
       </c>
       <c r="C16" t="n">
-        <v>8.678060656919255</v>
+        <v>10.3881277130386</v>
       </c>
       <c r="D16" t="n">
-        <v>7.238749800154134</v>
+        <v>6.905338462314874</v>
       </c>
       <c r="E16" t="n">
-        <v>18.52866186692865</v>
+        <v>19.3929140059312</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.132591633073092</v>
+        <v>1.685916062594878</v>
       </c>
       <c r="C17" t="n">
-        <v>8.125670493647746</v>
+        <v>9.839743080400423</v>
       </c>
       <c r="D17" t="n">
-        <v>6.804188996346327</v>
+        <v>6.439135929999193</v>
       </c>
       <c r="E17" t="n">
-        <v>17.06245112306717</v>
+        <v>17.96479507299449</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.476537123778919</v>
+        <v>1.925295605321378</v>
       </c>
       <c r="C18" t="n">
-        <v>9.551806296221875</v>
+        <v>11.66145448544672</v>
       </c>
       <c r="D18" t="n">
-        <v>7.311448217653611</v>
+        <v>6.952707789044783</v>
       </c>
       <c r="E18" t="n">
-        <v>19.3397916376544</v>
+        <v>20.53945787981288</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.526449177062827</v>
+        <v>1.926454067612389</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3060143350554</v>
+        <v>12.61991513414879</v>
       </c>
       <c r="D19" t="n">
-        <v>7.472160316838814</v>
+        <v>7.073983082950392</v>
       </c>
       <c r="E19" t="n">
-        <v>20.30462382895704</v>
+        <v>21.62035228471157</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.858584242886566</v>
+        <v>2.133161046741554</v>
       </c>
       <c r="C20" t="n">
-        <v>11.99350119397707</v>
+        <v>14.58676811979094</v>
       </c>
       <c r="D20" t="n">
-        <v>7.968944290141785</v>
+        <v>7.527148005753679</v>
       </c>
       <c r="E20" t="n">
-        <v>22.82102972700542</v>
+        <v>24.24707717228617</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.722338902422434</v>
+        <v>1.263254040962541</v>
       </c>
       <c r="C21" t="n">
-        <v>8.960470201522895</v>
+        <v>10.76384255945386</v>
       </c>
       <c r="D21" t="n">
-        <v>6.677219565756088</v>
+        <v>6.300788043516733</v>
       </c>
       <c r="E21" t="n">
-        <v>17.36002866970142</v>
+        <v>18.32788464393314</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_14_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.255298384839223</v>
+        <v>2.594729251776722</v>
       </c>
       <c r="C3" t="n">
-        <v>4.577483974161185</v>
+        <v>7.77021608920465</v>
       </c>
       <c r="D3" t="n">
-        <v>6.059204571128838</v>
+        <v>8.203511074174896</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89198693012925</v>
+        <v>18.56845641515627</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.373608914020839</v>
+        <v>1.080484330888188</v>
       </c>
       <c r="C4" t="n">
-        <v>4.987344346203179</v>
+        <v>4.633937996327428</v>
       </c>
       <c r="D4" t="n">
-        <v>6.284802482499808</v>
+        <v>5.824109759366618</v>
       </c>
       <c r="E4" t="n">
-        <v>12.64575574272383</v>
+        <v>11.53853208658223</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.541305363180241</v>
+        <v>1.181115046981787</v>
       </c>
       <c r="C5" t="n">
-        <v>5.499599223718398</v>
+        <v>5.408885818596488</v>
       </c>
       <c r="D5" t="n">
-        <v>6.68553925773211</v>
+        <v>6.131129786597719</v>
       </c>
       <c r="E5" t="n">
-        <v>13.72644384463075</v>
+        <v>12.72113065217599</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.736343191290071</v>
+        <v>1.291263149289368</v>
       </c>
       <c r="C6" t="n">
-        <v>6.114781582086863</v>
+        <v>6.386636611953013</v>
       </c>
       <c r="D6" t="n">
-        <v>7.01074124757204</v>
+        <v>6.508817083941728</v>
       </c>
       <c r="E6" t="n">
-        <v>14.86186602094897</v>
+        <v>14.18671684518411</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.960885738193804</v>
+        <v>1.403317091316642</v>
       </c>
       <c r="C7" t="n">
-        <v>6.845507867957046</v>
+        <v>7.535642145654386</v>
       </c>
       <c r="D7" t="n">
-        <v>7.391337445898849</v>
+        <v>6.855159177631121</v>
       </c>
       <c r="E7" t="n">
-        <v>16.1977310520497</v>
+        <v>15.79411841460215</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.203194432006626</v>
+        <v>1.523446763207152</v>
       </c>
       <c r="C8" t="n">
-        <v>4.48991607005977</v>
+        <v>8.829611932569746</v>
       </c>
       <c r="D8" t="n">
-        <v>5.594926502702007</v>
+        <v>7.22958767175127</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2880370047684</v>
+        <v>17.58264636752817</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.532094150949512</v>
+        <v>1.632925105892503</v>
       </c>
       <c r="C9" t="n">
-        <v>5.406742859549266</v>
+        <v>10.26652310298236</v>
       </c>
       <c r="D9" t="n">
-        <v>6.116643837009071</v>
+        <v>7.586774606135264</v>
       </c>
       <c r="E9" t="n">
-        <v>13.05548084750785</v>
+        <v>19.48622281501013</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.89154343689195</v>
+        <v>1.024443911904504</v>
       </c>
       <c r="C10" t="n">
-        <v>6.507998179385404</v>
+        <v>7.465052463460066</v>
       </c>
       <c r="D10" t="n">
-        <v>6.675835619135677</v>
+        <v>5.951786552134033</v>
       </c>
       <c r="E10" t="n">
-        <v>15.07537723541303</v>
+        <v>14.4412829274986</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.259165648631219</v>
+        <v>0.9547300074259382</v>
       </c>
       <c r="C11" t="n">
-        <v>7.774111961284961</v>
+        <v>8.04601148492516</v>
       </c>
       <c r="D11" t="n">
-        <v>7.221099829726083</v>
+        <v>5.777811041464456</v>
       </c>
       <c r="E11" t="n">
-        <v>17.25437743964226</v>
+        <v>14.77855253381555</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.644824784325983</v>
+        <v>1.024414459473377</v>
       </c>
       <c r="C12" t="n">
-        <v>9.233037132420291</v>
+        <v>9.603956734271463</v>
       </c>
       <c r="D12" t="n">
-        <v>7.750260484115673</v>
+        <v>6.150688637014436</v>
       </c>
       <c r="E12" t="n">
-        <v>19.62812240086195</v>
+        <v>16.77905983075928</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.018053089559555</v>
+        <v>0.8046502358777283</v>
       </c>
       <c r="C13" t="n">
-        <v>10.83037567169537</v>
+        <v>9.195363157240985</v>
       </c>
       <c r="D13" t="n">
-        <v>8.248282187601486</v>
+        <v>5.585025244781511</v>
       </c>
       <c r="E13" t="n">
-        <v>22.09671094885641</v>
+        <v>15.58503863790022</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.742906516826405</v>
+        <v>0.8637416301963438</v>
       </c>
       <c r="C14" t="n">
-        <v>7.757682001664914</v>
+        <v>10.88209407043039</v>
       </c>
       <c r="D14" t="n">
-        <v>6.280298968929101</v>
+        <v>5.942450131466646</v>
       </c>
       <c r="E14" t="n">
-        <v>15.78088748742042</v>
+        <v>17.68828583209338</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.798689421381709</v>
+        <v>0.8300185965554659</v>
       </c>
       <c r="C15" t="n">
-        <v>8.598745259893155</v>
+        <v>11.85682227859183</v>
       </c>
       <c r="D15" t="n">
-        <v>6.319470702328549</v>
+        <v>5.972265809244622</v>
       </c>
       <c r="E15" t="n">
-        <v>16.71690538360341</v>
+        <v>18.65910668439192</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.099447830577719</v>
+        <v>0.8999779379600935</v>
       </c>
       <c r="C16" t="n">
-        <v>10.3881277130386</v>
+        <v>13.86792263326438</v>
       </c>
       <c r="D16" t="n">
-        <v>6.905338462314874</v>
+        <v>6.360291771871131</v>
       </c>
       <c r="E16" t="n">
-        <v>19.3929140059312</v>
+        <v>21.12819234309561</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.685916062594878</v>
+        <v>0.5373596059194917</v>
       </c>
       <c r="C17" t="n">
-        <v>9.839743080400423</v>
+        <v>10.39255539518476</v>
       </c>
       <c r="D17" t="n">
-        <v>6.439135929999193</v>
+        <v>5.266291035120741</v>
       </c>
       <c r="E17" t="n">
-        <v>17.96479507299449</v>
+        <v>16.19620603622499</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.925295605321378</v>
+        <v>0.4204825417289089</v>
       </c>
       <c r="C18" t="n">
-        <v>11.66145448544672</v>
+        <v>9.367600974474048</v>
       </c>
       <c r="D18" t="n">
-        <v>6.952707789044783</v>
+        <v>4.777282503635404</v>
       </c>
       <c r="E18" t="n">
-        <v>20.53945787981288</v>
+        <v>14.56536601983836</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.926454067612389</v>
+        <v>0.4868977739212056</v>
       </c>
       <c r="C19" t="n">
-        <v>12.61991513414879</v>
+        <v>11.59404768807313</v>
       </c>
       <c r="D19" t="n">
-        <v>7.073983082950392</v>
+        <v>5.21728218972474</v>
       </c>
       <c r="E19" t="n">
-        <v>21.62035228471157</v>
+        <v>17.29822765171908</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.133161046741554</v>
+        <v>0.5494056502506002</v>
       </c>
       <c r="C20" t="n">
-        <v>14.58676811979094</v>
+        <v>13.89609879237626</v>
       </c>
       <c r="D20" t="n">
-        <v>7.527148005753679</v>
+        <v>5.657596035079434</v>
       </c>
       <c r="E20" t="n">
-        <v>24.24707717228617</v>
+        <v>20.1031004777063</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.263254040962541</v>
+        <v>0.6023316689865457</v>
       </c>
       <c r="C21" t="n">
-        <v>10.76384255945386</v>
+        <v>16.21614533209824</v>
       </c>
       <c r="D21" t="n">
-        <v>6.300788043516733</v>
+        <v>6.094071246910523</v>
       </c>
       <c r="E21" t="n">
-        <v>18.32788464393314</v>
+        <v>22.91254824799531</v>
       </c>
     </row>
   </sheetData>
